--- a/12621662.xlsx
+++ b/12621662.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/256b75f619a51fa0/Desktop/demo 1/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{AB07C150-AB71-4D33-A57D-FDABA29FBEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE0322A-ED55-4195-9D98-6DD78B738CF7}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{AB07C150-AB71-4D33-A57D-FDABA29FBEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BCAF2FA-8EA5-4077-A591-7CA988FC3382}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1067,7 +1067,7 @@
         <v>300</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" ref="I6:I69" si="1">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <f t="shared" ref="I7:I69" si="1">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>1330</v>
       </c>
       <c r="J7" s="15">
@@ -2509,21 +2509,21 @@
         <v>90</v>
       </c>
       <c r="F40" s="14">
+        <v>200</v>
+      </c>
+      <c r="G40" s="14">
         <v>4</v>
-      </c>
-      <c r="G40" s="14">
-        <v>200</v>
       </c>
       <c r="H40" s="14">
         <v>200</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="1"/>
-        <v>854</v>
+        <v>1050</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="0"/>
-        <v>586</v>
+        <v>390</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>49</v>
@@ -2537,245 +2537,487 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B41" s="14">
+        <v>480</v>
+      </c>
+      <c r="C41" s="14">
+        <v>20</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>90</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>200</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>20</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>90</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>180</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>20</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>90</v>
+      </c>
+      <c r="F43" s="14">
+        <v>150</v>
+      </c>
+      <c r="G43" s="14">
+        <v>3</v>
+      </c>
+      <c r="H43" s="14">
+        <v>200</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B44" s="14">
+        <v>480</v>
+      </c>
+      <c r="C44" s="14">
+        <v>20</v>
+      </c>
+      <c r="D44" s="14">
+        <v>180</v>
+      </c>
+      <c r="E44" s="14">
+        <v>90</v>
+      </c>
+      <c r="F44" s="14">
+        <v>250</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14">
+        <v>200</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>240</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>300</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B46" s="14">
+        <v>540</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>240</v>
+      </c>
+      <c r="E46" s="14">
+        <v>120</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>300</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>210</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B47" s="14">
+        <v>600</v>
+      </c>
+      <c r="C47" s="14">
+        <v>20</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>300</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B48" s="14">
+        <v>360</v>
+      </c>
+      <c r="C48" s="14">
+        <v>10</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>900</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>300</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B50" s="14">
+        <v>480</v>
+      </c>
+      <c r="C50" s="14">
+        <v>20</v>
+      </c>
+      <c r="D50" s="14">
+        <v>180</v>
+      </c>
+      <c r="E50" s="14">
+        <v>90</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>300</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14">
+        <v>180</v>
+      </c>
+      <c r="E51" s="14">
+        <v>90</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>360</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>310</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
